--- a/output/tablas_conteos.xlsx
+++ b/output/tablas_conteos.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01</t>
   </si>
   <si>
     <t xml:space="preserve">12</t>
@@ -652,19 +655,19 @@
         <v>10</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>22544223046.056</v>
+        <v>52566458291.8698</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>11152008110.625</v>
+        <v>19986617202.0342</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>678002899.148911</v>
+        <v>13377841551.6021</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>44410443192.963</v>
+        <v>91755075032.1376</v>
       </c>
     </row>
     <row r="3">
@@ -672,19 +675,19 @@
         <v>11</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>29931873643.743</v>
+        <v>22544223046.056</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>13005745768.7617</v>
+        <v>11152008110.625</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>4430950641.05066</v>
+        <v>678002899.148911</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>55432796646.4353</v>
+        <v>44410443192.963</v>
       </c>
     </row>
     <row r="4">
@@ -692,19 +695,19 @@
         <v>12</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>11236403267.1969</v>
+        <v>29931873643.743</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>7444172195.20106</v>
+        <v>13005745768.7617</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-3359704125.93419</v>
+        <v>4430950641.05066</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>25832510660.3279</v>
+        <v>55432796646.4353</v>
       </c>
     </row>
     <row r="5">
@@ -712,19 +715,19 @@
         <v>13</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>81868565319.0195</v>
+        <v>11236403267.1969</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>25119342277.7204</v>
+        <v>7444172195.20106</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>32615994594.395</v>
+        <v>-3359704125.93419</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>131121136043.644</v>
+        <v>25832510660.3279</v>
       </c>
     </row>
     <row r="6">
@@ -732,19 +735,19 @@
         <v>14</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>170711825949.867</v>
+        <v>81868563733.373</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>33576823598.2659</v>
+        <v>25119342279.4186</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>104876309211.492</v>
+        <v>32615993005.4186</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>236547342688.242</v>
+        <v>131121134461.327</v>
       </c>
     </row>
     <row r="7">
@@ -752,19 +755,19 @@
         <v>15</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>182641869345.036</v>
+        <v>170711825949.867</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>33180164801.0794</v>
+        <v>33576823598.2659</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>117584098506.453</v>
+        <v>104876309211.492</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>247699640183.62</v>
+        <v>236547342688.242</v>
       </c>
     </row>
     <row r="8">
@@ -772,19 +775,19 @@
         <v>16</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>43846516197.2389</v>
+        <v>182641869345.036</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>14139928642.513</v>
+        <v>33180164801.0794</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>16121752236.1931</v>
+        <v>117584098506.453</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>71571280158.2847</v>
+        <v>247699640183.62</v>
       </c>
     </row>
     <row r="9">
@@ -792,19 +795,19 @@
         <v>17</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8140845593.21935</v>
+        <v>43846516197.2389</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>4468893396.50222</v>
+        <v>14139928642.513</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-621505173.713572</v>
+        <v>16121752236.1931</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>16903196360.1523</v>
+        <v>71571280158.2847</v>
       </c>
     </row>
     <row r="10">
@@ -812,19 +815,19 @@
         <v>18</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>91100794977.893</v>
+        <v>8140845593.21935</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>23403380155.36</v>
+        <v>4468893396.50222</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>45212784712.6118</v>
+        <v>-621505173.713572</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>136988805243.174</v>
+        <v>16903196360.1523</v>
       </c>
     </row>
     <row r="11">
@@ -832,19 +835,19 @@
         <v>19</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>43950130273.8989</v>
+        <v>91100794977.893</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>16241554732.5368</v>
+        <v>23403380155.36</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>12104617987.0731</v>
+        <v>45212784712.6118</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>75795642560.7247</v>
+        <v>136988805243.174</v>
       </c>
     </row>
     <row r="12">
@@ -852,19 +855,19 @@
         <v>20</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>79993279671.9518</v>
+        <v>36833314053.2596</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>22129529575.4162</v>
+        <v>14605174676.944</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>36602962821.0771</v>
+        <v>8196322257.51086</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>123383596522.826</v>
+        <v>65470305849.0082</v>
       </c>
     </row>
     <row r="13">
@@ -872,19 +875,19 @@
         <v>21</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>122203703919.12</v>
+        <v>79993279671.9518</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>26835781216.1878</v>
+        <v>22129529575.4162</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>69585637821.3801</v>
+        <v>36602962821.0771</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>174821770016.86</v>
+        <v>123383596522.826</v>
       </c>
     </row>
     <row r="14">
@@ -892,19 +895,19 @@
         <v>22</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>24421392217.2812</v>
+        <v>122203703919.12</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>10534505318.5806</v>
+        <v>26835781216.1878</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3765936253.67028</v>
+        <v>69585637821.3801</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>45076848180.8922</v>
+        <v>174821770016.86</v>
       </c>
     </row>
     <row r="15">
@@ -912,19 +915,19 @@
         <v>23</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4046507918.07741</v>
+        <v>24421392217.2812</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3004397393.44436</v>
+        <v>10534505318.5806</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-1844342784.52009</v>
+        <v>3765936253.67028</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>9937358620.67492</v>
+        <v>45076848180.8922</v>
       </c>
     </row>
     <row r="16">
@@ -932,19 +935,19 @@
         <v>24</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>21315584794.0759</v>
+        <v>4046507918.07741</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>10759900209.3134</v>
+        <v>3004397393.44436</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>218187410.420898</v>
+        <v>-1844342784.52009</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>42412982177.731</v>
+        <v>9937358620.67492</v>
       </c>
     </row>
     <row r="17">
@@ -952,19 +955,19 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>65356032087.0157</v>
+        <v>21315584794.0759</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>18525311282.2517</v>
+        <v>10759900209.3134</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>29032660478.1158</v>
+        <v>218187410.420898</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>101679403695.916</v>
+        <v>42412982177.731</v>
       </c>
     </row>
     <row r="18">
@@ -972,19 +975,19 @@
         <v>26</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>27687736025.6277</v>
+        <v>65356032087.0157</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>10650276049.9308</v>
+        <v>18525311282.2517</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>6805283428.48129</v>
+        <v>29032660478.1158</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>48570188622.7741</v>
+        <v>101679403695.916</v>
       </c>
     </row>
     <row r="19">
@@ -992,19 +995,19 @@
         <v>27</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>56481390545.0189</v>
+        <v>27687736025.6277</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>18177012647.703</v>
+        <v>10650276049.9308</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>20840942992.8772</v>
+        <v>6805283428.48129</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>92121838097.1606</v>
+        <v>48570188622.7741</v>
       </c>
     </row>
     <row r="20">
@@ -1012,19 +1015,19 @@
         <v>28</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2544.95044079</v>
+        <v>56481390545.0189</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>795.17835334903</v>
+        <v>18177012647.703</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>985.810171351071</v>
+        <v>20840942992.8772</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>4104.09071022893</v>
+        <v>92121838097.1606</v>
       </c>
     </row>
     <row r="21">
@@ -1032,19 +1035,19 @@
         <v>29</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>235</v>
+        <v>14</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>190137473859.94</v>
+        <v>2544.95044079</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>31440359334.8548</v>
+        <v>795.17835334903</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>128491014146.661</v>
+        <v>985.810171351071</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>251783933573.219</v>
+        <v>4104.09071022893</v>
       </c>
     </row>
     <row r="22">
@@ -1052,19 +1055,19 @@
         <v>30</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>556</v>
+        <v>234</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>434883361049.404</v>
+        <v>183020660355.94</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>44638853703.4349</v>
+        <v>30638245962.0433</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>347358047894.823</v>
+        <v>122946938701.914</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>522408674203.986</v>
+        <v>243094382009.966</v>
       </c>
     </row>
     <row r="23">
@@ -1072,19 +1075,19 @@
         <v>31</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>70</v>
+        <v>556</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>71633439301.7105</v>
+        <v>434883361049.404</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>21078913768.9331</v>
+        <v>44638853703.4349</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>30303109879.6911</v>
+        <v>347358047894.823</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>112963768723.73</v>
+        <v>522408674203.986</v>
       </c>
     </row>
     <row r="24">
@@ -1092,19 +1095,19 @@
         <v>32</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>138665600376.025</v>
+        <v>71633439301.7105</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>28496209503.7993</v>
+        <v>21078913768.9331</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>82791861388.2629</v>
+        <v>30303109879.6911</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>194539339363.786</v>
+        <v>112963768723.73</v>
       </c>
     </row>
     <row r="25">
@@ -1112,19 +1115,19 @@
         <v>33</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>77486501274.2934</v>
+        <v>100332773394.441</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>23033305264.338</v>
+        <v>22715639008.2811</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>32324112704.9129</v>
+        <v>55793246664.7648</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>122648889843.674</v>
+        <v>144872300124.117</v>
       </c>
     </row>
     <row r="26">
@@ -1132,19 +1135,19 @@
         <v>34</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4333387198.35524</v>
+        <v>77486501274.2934</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>3382601739.83194</v>
+        <v>23033305264.338</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-2299024971.61144</v>
+        <v>32324112704.9129</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>10965799368.3219</v>
+        <v>122648889843.674</v>
       </c>
     </row>
     <row r="27">
@@ -1152,19 +1155,19 @@
         <v>35</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>45470244499.7315</v>
+        <v>4333387198.35524</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>13407499642.9347</v>
+        <v>3382601739.83194</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>19181585461.4843</v>
+        <v>-2299024971.61144</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>71758903537.9787</v>
+        <v>10965799368.3219</v>
       </c>
     </row>
     <row r="28">
@@ -1172,19 +1175,19 @@
         <v>36</v>
       </c>
       <c r="B28" s="4" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>113681735025.808</v>
+        <v>45470244499.7315</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>24461961073.5662</v>
+        <v>13407499642.9347</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>65718119795.825</v>
+        <v>19181585461.4843</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>161645350255.792</v>
+        <v>71758903537.9787</v>
       </c>
     </row>
     <row r="29">
@@ -1192,19 +1195,19 @@
         <v>37</v>
       </c>
       <c r="B29" s="4" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>18188606791.4543</v>
+        <v>113681735025.808</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>9674748204.70021</v>
+        <v>24461961073.5662</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-781086559.854916</v>
+        <v>65718119795.825</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>37158300142.7635</v>
+        <v>161645350255.792</v>
       </c>
     </row>
     <row r="30">
@@ -1212,19 +1215,19 @@
         <v>38</v>
       </c>
       <c r="B30" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>15367643115.4186</v>
+        <v>18188606791.4543</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>6475264302.22627</v>
+        <v>9674748204.70021</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2671314944.08323</v>
+        <v>-781086559.854916</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>28063971286.7539</v>
+        <v>37158300142.7635</v>
       </c>
     </row>
     <row r="31">
@@ -1232,19 +1235,19 @@
         <v>39</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>57910053830.7463</v>
+        <v>15367643115.4186</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>17323633407.533</v>
+        <v>6475264302.22627</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>23942863520.6416</v>
+        <v>2671314944.08323</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>91877244140.851</v>
+        <v>28063971286.7539</v>
       </c>
     </row>
     <row r="32">
@@ -1252,19 +1255,19 @@
         <v>40</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>41073362086.4487</v>
+        <v>57910053830.7463</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>15973023065.193</v>
+        <v>17323633407.533</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>9754371345.90474</v>
+        <v>23942863520.6416</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>72392352826.9927</v>
+        <v>91877244140.851</v>
       </c>
     </row>
     <row r="33">
@@ -1272,19 +1275,19 @@
         <v>41</v>
       </c>
       <c r="B33" s="4" t="n">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>178918743386.583</v>
+        <v>41073362086.4487</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>28820256230.6034</v>
+        <v>15973023065.193</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>122409632096.73</v>
+        <v>9754371345.90474</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>235427854676.435</v>
+        <v>72392352826.9927</v>
       </c>
     </row>
     <row r="34">
@@ -1292,19 +1295,19 @@
         <v>42</v>
       </c>
       <c r="B34" s="4" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>166553928658.093</v>
+        <v>178918743386.583</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>32511099983.5537</v>
+        <v>28820256230.6034</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>102808021875.511</v>
+        <v>122409632096.73</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>230299835440.674</v>
+        <v>235427854676.435</v>
       </c>
     </row>
     <row r="35">
@@ -1312,19 +1315,19 @@
         <v>43</v>
       </c>
       <c r="B35" s="4" t="n">
-        <v>47</v>
+        <v>187</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>52503934553.3019</v>
+        <v>166553928658.093</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>15452971683.1165</v>
+        <v>32511099983.5537</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>22204630840.9043</v>
+        <v>102808021875.511</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>82803238265.6995</v>
+        <v>230299835440.674</v>
       </c>
     </row>
     <row r="36">
@@ -1332,19 +1335,19 @@
         <v>44</v>
       </c>
       <c r="B36" s="4" t="n">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>90334721312.6798</v>
+        <v>52503934553.3019</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>16521255039.8159</v>
+        <v>15452971683.1165</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>57940788648.6937</v>
+        <v>22204630840.9043</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>122728653976.666</v>
+        <v>82803238265.6995</v>
       </c>
     </row>
     <row r="37">
@@ -1352,19 +1355,19 @@
         <v>45</v>
       </c>
       <c r="B37" s="4" t="n">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>6404904631.5031</v>
+        <v>90334721312.6798</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>3857763802.6266</v>
+        <v>16521255039.8159</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>-1159178154.86381</v>
+        <v>57940788648.6937</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>13968987417.87</v>
+        <v>122728653976.666</v>
       </c>
     </row>
     <row r="38">
@@ -1372,19 +1375,19 @@
         <v>46</v>
       </c>
       <c r="B38" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>9879783085.4885</v>
+        <v>6404904631.5031</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>7113475582.57486</v>
+        <v>3857763802.6266</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-4067913289.48419</v>
+        <v>-1159178154.86381</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>23827479460.4612</v>
+        <v>13968987417.87</v>
       </c>
     </row>
     <row r="39">
@@ -1392,34 +1395,54 @@
         <v>47</v>
       </c>
       <c r="B39" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>18453381722.3662</v>
+        <v>9879783085.4885</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>7407918405.28554</v>
+        <v>7113475582.57486</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>3928358688.53517</v>
+        <v>-4067913289.48419</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>32978404756.1973</v>
+        <v>23827479460.4612</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>18453381722.3662</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>7407918405.28554</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>3928358688.53517</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>32978404756.1973</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B41" s="4" t="n">
         <v>3048</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C41" s="4" t="n">
         <v>2819359483095.64</v>
       </c>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
